--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -28054,6 +28054,154 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28087,7 +28235,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -28170,7 +28318,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -28180,7 +28328,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -28232,7 +28380,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -1850,9 +1844,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1989,6 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -2146,9 +2134,6 @@
       <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -2791,7 +2776,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2923,6 @@
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -4962,9 +4944,6 @@
       <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5503,9 +5482,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -5899,9 +5875,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -6047,9 +6020,6 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -6195,9 +6165,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -6840,7 +6807,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -6987,9 +6954,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -8863,9 +8827,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9404,9 +9365,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -9800,9 +9758,6 @@
       <c r="O55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -9948,9 +9903,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10096,9 +10048,6 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -10741,7 +10690,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -10888,9 +10837,6 @@
       <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -12616,9 +12562,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12764,9 +12707,6 @@
       <c r="O73" t="n">
         <v>6</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13305,9 +13245,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -13701,9 +13638,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -13849,9 +13783,6 @@
       <c r="O79" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -13997,9 +13928,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -14393,9 +14321,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -14642,7 +14567,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -14789,9 +14714,6 @@
       <c r="O84" t="n">
         <v>3</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -15185,9 +15107,6 @@
       <c r="O86" t="n">
         <v>3</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -16517,9 +16436,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -16665,9 +16581,6 @@
       <c r="O96" t="n">
         <v>4</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17206,9 +17119,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -17602,9 +17512,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -17750,9 +17657,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17898,9 +17802,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -18294,9 +18195,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18543,7 +18441,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -18690,9 +18588,6 @@
       <c r="O107" t="n">
         <v>5</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -19086,9 +18981,6 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -20566,9 +20458,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -20714,9 +20603,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21010,9 +20896,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21406,9 +21289,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21554,9 +21434,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -21702,9 +21579,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -22098,9 +21972,6 @@
       <c r="O128" t="n">
         <v>3</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -22347,7 +22218,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22494,9 +22365,6 @@
       <c r="O130" t="n">
         <v>4</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -22890,9 +22758,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23038,9 +22903,6 @@
       <c r="O133" t="n">
         <v>2</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -23186,9 +23048,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -23334,9 +23193,6 @@
       <c r="O135" t="n">
         <v>4</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -23482,9 +23338,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -23630,9 +23483,6 @@
       <c r="O137" t="n">
         <v>2</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -23778,9 +23628,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -23926,9 +23773,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -24074,9 +23918,6 @@
       <c r="O140" t="n">
         <v>5</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01836405909759895</v>
       </c>
@@ -24222,9 +24063,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -24618,9 +24456,6 @@
       <c r="O143" t="n">
         <v>2</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -24766,9 +24601,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25162,9 +24994,6 @@
       <c r="O146" t="n">
         <v>4</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -25558,9 +25387,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -25706,9 +25532,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -25854,9 +25677,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -26002,9 +25822,6 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -26150,9 +25967,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -26298,9 +26112,6 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -26446,9 +26257,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -26594,9 +26402,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26742,9 +26547,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -26890,9 +26692,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -27038,9 +26837,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27434,9 +27230,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -27582,9 +27375,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -27978,9 +27768,6 @@
       <c r="O163" t="n">
         <v>6</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -28126,9 +27913,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -28199,6 +27983,151 @@
       <c r="BC164" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="n">
+        <v>2</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28235,7 +28164,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28247,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -28328,7 +28257,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -28380,7 +28309,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -16576,10 +16576,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16732,10 +16732,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -20704,12 +20704,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20743,84 +20743,92 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O121" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.001203187096679587</v>
+        <v>3</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_MENINGOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_MENINGOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20847,17 +20855,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20891,22 +20899,39 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_MENINGOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_MENINGOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Meningococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -20914,6 +20939,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary invasive meningococcal disease notifications combining confirmed and probable cases under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20926,12 +21009,12 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_MENINGOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -20939,47 +21022,47 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21006,17 +21089,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21050,170 +21133,84 @@
         </is>
       </c>
       <c r="N123" t="n">
+        <v>17</v>
+      </c>
+      <c r="O123" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q123" t="n">
         <v>0</v>
       </c>
-      <c r="O123" t="n">
+      <c r="R123" t="n">
+        <v>0.001203187096679587</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
         <v>0</v>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP123" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT123" t="n">
-        <v>1</v>
-      </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -21245,12 +21242,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21297,68 +21294,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21385,17 +21396,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21434,76 +21445,165 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21535,12 +21635,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21574,95 +21674,81 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21689,17 +21775,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21733,170 +21819,81 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21928,12 +21925,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21967,13 +21964,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>0.05673781399415487</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21982,7 +21979,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -22007,7 +22004,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22020,42 +22017,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22087,12 +22084,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22126,29 +22123,29 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Syst. meningokokksykdom</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -22158,7 +22155,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -22173,7 +22170,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -22208,17 +22205,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22241,7 +22238,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22254,42 +22251,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22321,12 +22318,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22360,13 +22357,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>0.03737952171313338</v>
+        <v>0.05673781399415487</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22375,7 +22372,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -22400,7 +22397,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -22413,42 +22410,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22480,12 +22477,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22519,29 +22516,29 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>Invasiv meningokockinfektion</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -22551,7 +22548,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -22566,7 +22563,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -22601,17 +22598,17 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -22634,7 +22631,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -22647,42 +22644,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22714,12 +22711,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22744,7 +22741,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22753,81 +22750,95 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.03737952171313338</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22854,17 +22865,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22889,7 +22900,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22898,81 +22909,170 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23034,7 +23134,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23043,13 +23143,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23179,7 +23279,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23188,13 +23288,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R135" t="n">
-        <v>0.001146015253107754</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23324,7 +23424,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23333,13 +23433,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23469,7 +23569,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23478,13 +23578,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.001146015253107754</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23614,7 +23714,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23623,13 +23723,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23759,7 +23859,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23768,13 +23868,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R139" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23874,12 +23974,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23904,22 +24004,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R140" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23952,42 +24052,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24019,12 +24119,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24049,104 +24149,90 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
         <v>0</v>
       </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT141" t="n">
-        <v>1</v>
-      </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24173,17 +24259,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24217,170 +24303,81 @@
         </is>
       </c>
       <c r="N142" t="n">
+        <v>5</v>
+      </c>
+      <c r="O142" t="n">
+        <v>5</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.01836405909759895</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
         <v>0</v>
       </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV142" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24412,12 +24409,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24451,81 +24448,95 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24552,17 +24563,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24601,17 +24612,34 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -24619,6 +24647,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24631,12 +24717,12 @@
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -24644,47 +24730,47 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24711,17 +24797,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24755,170 +24841,81 @@
         </is>
       </c>
       <c r="N145" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" t="n">
+        <v>2</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
         <v>0</v>
       </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP145" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT145" t="n">
-        <v>1</v>
-      </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24950,12 +24947,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24989,13 +24986,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0.03737952171313338</v>
+        <v>0</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25004,7 +25001,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -25029,7 +25026,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -25042,42 +25039,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25109,12 +25106,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25148,29 +25145,29 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Invasiv meningokockinfektion</t>
+          <t>Syst. meningokokksykdom</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -25195,7 +25192,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -25230,17 +25227,17 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -25263,7 +25260,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -25276,42 +25273,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25343,12 +25340,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25373,7 +25370,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25382,81 +25379,95 @@
         </is>
       </c>
       <c r="N148" t="n">
+        <v>4</v>
+      </c>
+      <c r="O148" t="n">
+        <v>4</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
         <v>1</v>
       </c>
-      <c r="O148" t="n">
-        <v>1</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP148" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
-      <c r="AT148" t="n">
-        <v>0</v>
-      </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25483,17 +25494,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25518,7 +25529,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25527,81 +25538,170 @@
         </is>
       </c>
       <c r="N149" t="n">
+        <v>4</v>
+      </c>
+      <c r="O149" t="n">
+        <v>4</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
         <v>1</v>
       </c>
-      <c r="O149" t="n">
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
         <v>1</v>
       </c>
-      <c r="R149" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP149" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
-      <c r="AT149" t="n">
-        <v>0</v>
-      </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25663,7 +25763,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25672,13 +25772,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25808,7 +25908,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25817,13 +25917,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25953,7 +26053,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25962,13 +26062,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26098,7 +26198,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26107,13 +26207,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R153" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26243,7 +26343,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26388,7 +26488,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26397,13 +26497,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26533,7 +26633,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26648,12 +26748,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26678,12 +26778,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N157" t="n">
@@ -26726,42 +26826,42 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26793,12 +26893,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26823,104 +26923,90 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
         <v>0</v>
       </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT158" t="n">
-        <v>1</v>
-      </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26947,17 +27033,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26996,165 +27082,76 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT159" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV159" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27186,12 +27183,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27238,68 +27235,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27326,17 +27337,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27375,17 +27386,34 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -27393,6 +27421,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27405,12 +27491,12 @@
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -27418,47 +27504,47 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27485,17 +27571,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27534,165 +27620,76 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27724,12 +27721,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27763,81 +27760,95 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>0.001719022879661631</v>
+        <v>0</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27864,17 +27875,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27899,7 +27910,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -27908,81 +27919,170 @@
         </is>
       </c>
       <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
         <v>1</v>
       </c>
-      <c r="O164" t="n">
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
         <v>1</v>
       </c>
-      <c r="R164" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
-      <c r="AT164" t="n">
-        <v>0</v>
-      </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28144,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28053,13 +28153,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O165" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R165" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28126,6 +28226,296 @@
         </is>
       </c>
       <c r="BC165" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="n">
+        <v>1</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>2</v>
+      </c>
+      <c r="O167" t="n">
+        <v>2</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -28247,7 +28637,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -28257,7 +28647,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28277,7 +28667,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -28309,7 +28699,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -28521,6 +28521,151 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>1</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28554,7 +28699,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -28637,7 +28782,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -28647,7 +28792,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -28699,7 +28844,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -24409,12 +24409,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24448,95 +24448,84 @@
         </is>
       </c>
       <c r="N143" t="n">
+        <v>18</v>
+      </c>
+      <c r="O143" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q143" t="n">
         <v>0</v>
       </c>
-      <c r="O143" t="n">
+      <c r="R143" t="n">
+        <v>0.001273962808248974</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
         <v>0</v>
       </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT143" t="n">
-        <v>1</v>
-      </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -24563,7 +24552,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -24612,98 +24601,23 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -24797,17 +24711,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24841,81 +24755,170 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>2</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24947,12 +24950,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24986,95 +24989,81 @@
         </is>
       </c>
       <c r="N146" t="n">
+        <v>2</v>
+      </c>
+      <c r="O146" t="n">
+        <v>2</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
         <v>0</v>
       </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT146" t="n">
-        <v>1</v>
-      </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25090,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -25150,98 +25139,23 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -25335,17 +25249,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25379,22 +25293,39 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>4</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.03737952171313338</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -25402,6 +25333,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -25419,7 +25408,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -25432,42 +25421,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25483,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -25543,98 +25532,23 @@
       <c r="O149" t="n">
         <v>4</v>
       </c>
+      <c r="R149" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Invasiv meningokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -25728,17 +25642,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25763,7 +25677,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25772,81 +25686,170 @@
         </is>
       </c>
       <c r="N150" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" t="n">
+        <v>4</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
         <v>1</v>
       </c>
-      <c r="O150" t="n">
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
         <v>1</v>
       </c>
-      <c r="R150" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP150" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25878,12 +25881,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25923,7 +25926,7 @@
         <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25956,42 +25959,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26023,12 +26026,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26053,7 +26056,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26062,13 +26065,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26101,42 +26104,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26168,12 +26171,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26207,13 +26210,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26246,42 +26249,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26313,12 +26316,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26343,7 +26346,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26352,13 +26355,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R154" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26391,42 +26394,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26458,12 +26461,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26503,7 +26506,7 @@
         <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26536,42 +26539,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26603,12 +26606,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26633,7 +26636,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26648,7 +26651,7 @@
         <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26681,42 +26684,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26748,12 +26751,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26787,13 +26790,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26826,42 +26829,42 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26893,12 +26896,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26923,7 +26926,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -26932,13 +26935,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -26971,42 +26974,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27038,12 +27041,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27068,22 +27071,22 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27116,42 +27119,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27183,12 +27186,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27235,82 +27238,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27337,7 +27326,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -27386,98 +27375,23 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U161" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -27571,17 +27485,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27620,76 +27534,165 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27721,12 +27724,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27773,82 +27776,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27875,7 +27864,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -27924,98 +27913,23 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -28109,17 +28023,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28153,81 +28067,170 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>6</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28259,12 +28262,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28289,7 +28292,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28298,13 +28301,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O166" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R166" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28337,42 +28340,42 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28404,12 +28407,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28434,7 +28437,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28443,13 +28446,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -28482,42 +28485,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28549,12 +28552,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28579,7 +28582,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28588,13 +28591,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R168" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28627,40 +28630,185 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>1</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW168" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX168" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY168" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ168" t="inlineStr">
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA168" t="inlineStr">
+      <c r="BA169" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB168" t="inlineStr">
+      <c r="BB169" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC168" t="inlineStr">
+      <c r="BC169" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -28782,7 +28930,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -28792,7 +28940,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -28844,7 +28992,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -25488,12 +25488,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25527,13 +25527,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O149" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R149" t="n">
-        <v>0.03737952171313338</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -25580,42 +25580,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25647,12 +25647,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25686,29 +25686,29 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O150" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>Invasiv meningokockinfektion</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -25733,7 +25733,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -25768,17 +25768,17 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -25814,42 +25814,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25881,12 +25881,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25920,81 +25920,95 @@
         </is>
       </c>
       <c r="N151" t="n">
+        <v>4</v>
+      </c>
+      <c r="O151" t="n">
+        <v>4</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
         <v>1</v>
       </c>
-      <c r="O151" t="n">
-        <v>1</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP151" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
-      <c r="AT151" t="n">
-        <v>0</v>
-      </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26021,17 +26035,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26056,7 +26070,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26065,81 +26079,170 @@
         </is>
       </c>
       <c r="N152" t="n">
+        <v>4</v>
+      </c>
+      <c r="O152" t="n">
+        <v>4</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
         <v>1</v>
       </c>
-      <c r="O152" t="n">
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
         <v>1</v>
       </c>
-      <c r="R152" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
-      <c r="AT152" t="n">
-        <v>0</v>
-      </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26201,7 +26304,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26210,13 +26313,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26346,7 +26449,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26355,13 +26458,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R154" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26491,7 +26594,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26500,13 +26603,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26636,7 +26739,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26645,13 +26748,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26781,7 +26884,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26926,7 +27029,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -26935,13 +27038,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27071,7 +27174,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27186,12 +27289,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27216,12 +27319,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N160" t="n">
@@ -27264,42 +27367,42 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27331,12 +27434,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27361,104 +27464,90 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
         <v>0</v>
       </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT161" t="n">
-        <v>1</v>
-      </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27485,17 +27574,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27534,165 +27623,76 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV162" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27724,12 +27724,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27776,68 +27776,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27864,17 +27878,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27913,17 +27927,34 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -27931,6 +27962,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27943,12 +28032,12 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -27956,47 +28045,47 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28023,17 +28112,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28072,165 +28161,76 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28262,12 +28262,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28301,81 +28301,95 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>0.001719022879661631</v>
+        <v>0</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28402,17 +28416,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28437,7 +28451,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28446,81 +28460,170 @@
         </is>
       </c>
       <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
         <v>1</v>
       </c>
-      <c r="O167" t="n">
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
         <v>1</v>
       </c>
-      <c r="R167" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
-      <c r="AT167" t="n">
-        <v>0</v>
-      </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28582,7 +28685,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28591,13 +28694,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O168" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R168" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28727,7 +28830,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28809,6 +28912,441 @@
         </is>
       </c>
       <c r="BC169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="n">
+        <v>2</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>1</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -28847,7 +29385,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -28930,7 +29468,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -28940,7 +29478,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -28960,7 +29498,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -28992,7 +29530,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -35194,12 +35194,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35233,13 +35233,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -35272,42 +35272,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35339,12 +35339,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35378,95 +35378,81 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35493,7 +35479,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -35542,98 +35528,23 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -35727,17 +35638,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35771,22 +35682,39 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>10</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0.1891260466471829</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -35794,6 +35722,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35811,7 +35797,7 @@
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
@@ -35824,42 +35810,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35886,7 +35872,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -35935,98 +35921,23 @@
       <c r="O202" t="n">
         <v>10</v>
       </c>
+      <c r="R202" t="n">
+        <v>0.1891260466471829</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -36120,17 +36031,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36164,22 +36075,39 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O203" t="n">
-        <v>4</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.03737952171313338</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -36187,6 +36115,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36204,7 +36190,7 @@
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT203" t="n">
@@ -36217,42 +36203,42 @@
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36279,7 +36265,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -36328,98 +36314,23 @@
       <c r="O204" t="n">
         <v>4</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Invasiv meningokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -36513,17 +36424,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36548,7 +36459,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36557,81 +36468,170 @@
         </is>
       </c>
       <c r="N205" t="n">
+        <v>4</v>
+      </c>
+      <c r="O205" t="n">
+        <v>4</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
         <v>1</v>
       </c>
-      <c r="O205" t="n">
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT205" t="n">
         <v>1</v>
       </c>
-      <c r="R205" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO205" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP205" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
-      <c r="AT205" t="n">
-        <v>0</v>
-      </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36663,12 +36663,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36708,7 +36708,7 @@
         <v>1</v>
       </c>
       <c r="R206" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -36741,42 +36741,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36808,12 +36808,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36838,7 +36838,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -36847,93 +36847,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36948,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -37012,98 +37000,18 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -37197,17 +37105,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -37232,7 +37140,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -37246,76 +37154,168 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37347,12 +37347,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37386,13 +37386,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -37425,42 +37425,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37492,12 +37492,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37522,7 +37522,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37531,93 +37531,81 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37632,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -37696,98 +37684,18 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -37881,17 +37789,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37916,7 +37824,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -37925,81 +37833,173 @@
         </is>
       </c>
       <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
         <v>1</v>
       </c>
-      <c r="O213" t="n">
-        <v>1</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38031,12 +38031,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38076,7 +38076,7 @@
         <v>1</v>
       </c>
       <c r="R214" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -38109,42 +38109,42 @@
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38176,12 +38176,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -38206,7 +38206,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -38220,88 +38220,76 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="P215" t="n">
-        <v>1</v>
-      </c>
       <c r="R215" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38328,7 +38316,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -38380,98 +38368,18 @@
       <c r="P216" t="n">
         <v>1</v>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R216" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -38565,17 +38473,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38600,7 +38508,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -38614,76 +38522,168 @@
       <c r="O217" t="n">
         <v>1</v>
       </c>
-      <c r="R217" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P217" t="n">
+        <v>1</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38715,12 +38715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38754,13 +38754,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -38793,42 +38793,42 @@
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38860,12 +38860,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -38890,7 +38890,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -38899,13 +38899,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -38938,42 +38938,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39005,12 +39005,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39044,93 +39044,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39157,7 +39145,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -39209,98 +39197,18 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -39394,17 +39302,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39429,12 +39337,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -39443,76 +39351,168 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39544,12 +39544,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39596,82 +39596,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39698,7 +39684,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -39747,98 +39733,23 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -39932,17 +39843,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -39981,76 +39892,165 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40082,12 +40082,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40134,82 +40134,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40222,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -40285,98 +40271,23 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -40470,17 +40381,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40514,81 +40425,170 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>6</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40620,12 +40620,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -40659,13 +40659,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O229" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R229" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -40698,42 +40698,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40765,12 +40765,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40804,93 +40804,81 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>0</v>
-      </c>
-      <c r="P230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40917,7 +40905,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -40969,98 +40957,18 @@
       <c r="P231" t="n">
         <v>0</v>
       </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN231" t="b">
-        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
@@ -41154,17 +41062,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41189,7 +41097,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -41198,81 +41106,173 @@
         </is>
       </c>
       <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
         <v>2</v>
       </c>
-      <c r="O232" t="n">
-        <v>2</v>
-      </c>
-      <c r="R232" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP232" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
-      <c r="AT232" t="n">
-        <v>0</v>
-      </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41304,12 +41304,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41334,7 +41334,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -41343,13 +41343,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R233" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -41382,42 +41382,42 @@
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41449,12 +41449,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41488,93 +41488,81 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
-        <v>0</v>
-      </c>
-      <c r="P234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41589,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -41653,98 +41641,18 @@
       <c r="P235" t="n">
         <v>0</v>
       </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -41838,17 +41746,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -41873,7 +41781,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -41887,76 +41795,168 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="R236" t="n">
-        <v>0</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41988,12 +41988,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42027,93 +42027,81 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
-        <v>1</v>
-      </c>
-      <c r="P237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42140,7 +42128,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -42192,98 +42180,18 @@
       <c r="P238" t="n">
         <v>1</v>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R238" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -42377,17 +42285,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42412,7 +42320,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -42426,74 +42334,311 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="R239" t="n">
+      <c r="P239" t="n">
+        <v>1</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" t="n">
+        <v>1</v>
+      </c>
+      <c r="R240" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S239" t="inlineStr">
+      <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO239" t="inlineStr">
+      <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP239" t="inlineStr">
+      <c r="AP240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR239" t="inlineStr">
+      <c r="AR240" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS239" t="inlineStr"/>
-      <c r="AT239" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU239" t="inlineStr">
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU240" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV239" t="inlineStr">
+      <c r="AV240" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW239" t="inlineStr">
+      <c r="AW240" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX239" t="inlineStr">
+      <c r="AX240" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY239" t="inlineStr">
+      <c r="AY240" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ239" t="inlineStr">
+      <c r="AZ240" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA239" t="inlineStr">
+      <c r="BA240" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB239" t="inlineStr">
+      <c r="BB240" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC239" t="inlineStr">
+      <c r="BC240" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -42615,7 +42760,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -42625,7 +42770,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1484,17 +1484,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1710,7 +1715,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1718,17 +1723,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2159,7 +2169,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2167,17 +2177,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2393,7 +2408,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2401,17 +2416,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2948,7 +2968,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2956,17 +2976,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3182,7 +3207,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3190,17 +3215,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -7083,7 +7113,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7091,17 +7121,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7317,7 +7352,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7325,17 +7360,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7766,7 +7806,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7774,17 +7814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8000,7 +8045,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8008,17 +8053,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8555,7 +8605,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8563,17 +8613,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8789,7 +8844,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8797,17 +8852,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -12542,7 +12602,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -12550,17 +12610,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -12776,7 +12841,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12784,17 +12849,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -13225,7 +13295,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -13233,17 +13303,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -13459,7 +13534,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -13467,17 +13542,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -14014,7 +14094,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -14022,17 +14102,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -14248,7 +14333,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -14256,17 +14341,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -18392,7 +18482,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -18400,17 +18490,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -18626,7 +18721,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18634,17 +18729,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -19075,7 +19175,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -19083,17 +19183,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -19309,7 +19414,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -19317,17 +19422,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -19861,7 +19971,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -19869,17 +19979,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -20095,7 +20210,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -20103,17 +20218,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -23842,7 +23962,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23850,17 +23970,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -24076,7 +24201,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -24084,17 +24209,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -24525,7 +24655,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24533,17 +24663,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -24759,7 +24894,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24767,17 +24902,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -25311,7 +25451,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -25319,17 +25459,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -25545,7 +25690,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -25553,17 +25698,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -29979,7 +30129,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
@@ -29987,17 +30137,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS168" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -30213,7 +30368,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
@@ -30221,17 +30376,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS169" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -30662,7 +30822,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -30670,17 +30830,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -30896,7 +31061,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -30904,17 +31069,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS173" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -31448,7 +31618,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -31456,17 +31626,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -31682,7 +31857,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -31690,17 +31865,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS177" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -34870,7 +35050,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -34878,17 +35058,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -35104,7 +35289,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -35112,17 +35297,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS197" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -35553,7 +35743,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -35561,17 +35751,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -35787,7 +35982,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -35795,17 +35990,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -36339,7 +36539,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -36347,17 +36547,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS204" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -36573,7 +36778,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -36581,17 +36786,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS205" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -39758,7 +39968,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -39766,17 +39976,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS224" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -39992,7 +40207,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -40000,17 +40215,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS225" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -40296,7 +40516,7 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
@@ -40304,17 +40524,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS227" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -40530,7 +40755,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -40538,17 +40763,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS228" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -41355,13 +41355,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O234" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R234" t="n">
-        <v>0.04774655365375727</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -45897,13 +45897,13 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
